--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_19283.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_19283.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Peea</t>
+          <t>Ile</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CYEA</t>
+          <t>RIE LU</t>
         </is>
       </c>
     </row>
